--- a/expert-system/output/reports/reports.xlsx
+++ b/expert-system/output/reports/reports.xlsx
@@ -11,23 +11,24 @@
     <sheet name="Feature Matrix" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Risk Assessment" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="TS-RPT-CRUD" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="TS-RPT-Confirmation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="TS-RPT-Periods" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TS-RPT-Locks" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TS-RPT-Statistics" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="TS-RPT-Permissions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TS-RPT-APIErrors" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="TS-RPT-Periods" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="TS-RPT-Locks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="TS-RPT-Statistics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TS-RPT-Permissions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TS-RPT-APIErrors" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Test Data" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="TS-RPT-Confirmation" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Feature Matrix'!$A$1:$I$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Risk Assessment'!$A$1:$F$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TS-RPT-CRUD'!$A$3:$J$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TS-RPT-Confirmation'!$A$3:$J$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'TS-RPT-Periods'!$A$3:$J$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'TS-RPT-Locks'!$A$3:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'TS-RPT-Statistics'!$A$3:$J$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'TS-RPT-Permissions'!$A$3:$J$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'TS-RPT-APIErrors'!$A$3:$J$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TS-RPT-Periods'!$A$3:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'TS-RPT-Locks'!$A$3:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'TS-RPT-Statistics'!$A$3:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'TS-RPT-Permissions'!$A$3:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'TS-RPT-APIErrors'!$A$3:$J$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'TS-RPT-Confirmation'!$A$3:$J$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,8 +89,12 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -138,8 +143,14 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+        <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -161,11 +172,55 @@
         <color rgb="00B4C6E7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -212,6 +267,15 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -578,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A63"/>
+  <dimension ref="A1:A65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -987,6 +1051,13 @@
       <c r="A63" s="7" t="inlineStr">
         <is>
           <t>Total: 110 test cases across 7 test suites</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Test Data Reference</t>
         </is>
       </c>
     </row>
@@ -999,6 +1070,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1007,11 +1079,789 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Reports Module Test Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>1. Recommended Test Users (Module-Specific)</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="n"/>
+      <c r="C4" s="24" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>User / Query</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Use Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Use alsmirnov</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Create/edit reports as regular employee</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Use kcherenkov</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Approve/reject reports as project manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Use juliet_nekhor</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>VIEW_ALL</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>View all reports read-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>2. Common Multi-Role Test Users (All Modules)</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="24" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Best For</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>perekrest</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, CHIEF_ACCOUNTANT, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Best multi-role user (7 roles). Use for cross-role permission testing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>pvaynmaster</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, CHIEF_OFFICER, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Multi-role with CHIEF_OFFICER. Use for highest-privilege scenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>ilnitsky</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Admin+accountant combo. Use for accounting and admin tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Same role set as ilnitsky. Use as second admin/accountant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>juliet_nekhor</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>DEPT_MGR, EMPLOYEE, HR, PM, VIEW_ALL</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Has VIEW_ALL. Use for read-only permission tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>kcherenkov</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>DEPT_MGR, EMPLOYEE, PM, TECH_LEAD</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Tech Lead + PM. Use for planner/project management tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>alsmirnov</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>EMPLOYEE-only. Use as minimum-privilege baseline user.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>3. Common SQL Queries (User Discovery)</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="24" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>SQL Query</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Find EMPLOYEE-only users (minimum privilege)</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true
+GROUP BY e.id
+HAVING COUNT(*) = 1 AND MAX(r.role) = 'ROLE_EMPLOYEE'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Find active contractors</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_CONTRACTOR'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Find active project managers</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_PROJECT_MANAGER'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Find active accountants</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_ACCOUNTANT'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Find active admins</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_ADMIN'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Get current report/approve periods per office</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>SELECT o.id as office_id, o.name,
+       rp.start as report_period_start,
+       ap.start as approve_period_start
+FROM office o
+JOIN office_period rp ON o.report_period_id = rp.id
+JOIN office_period ap ON o.approve_period_id = ap.id
+ORDER BY o.id;</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>ttt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>4. Module-Specific SQL Queries</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="24" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>SQL Query</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Find employees with active project/task assignments</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, p.name as project_name, t.name as task_name, t.id as task_id
+FROM ttt_backend.employee e
+JOIN ttt_backend.employee_project ep ON e.id = ep.employee_id
+JOIN ttt_backend.project p ON ep.project_id = p.id
+JOIN ttt_backend.task t ON t.project_id = p.id
+WHERE e.enabled = true AND p.status = 'ACTIVE'
+AND e.login = 'alsmirnov'
+LIMIT 10;</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Find valid task IDs for report creation</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>SELECT t.id, t.name, p.name as project_name
+FROM ttt_backend.task t
+JOIN ttt_backend.project p ON t.project_id = p.id
+JOIN ttt_backend.employee_project ep ON p.id = ep.project_id
+JOIN ttt_backend.employee e ON ep.employee_id = e.id
+WHERE e.enabled = true AND p.status = 'ACTIVE'
+AND e.login = '&lt;target_login&gt;'
+LIMIT 10;</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Find reports in REPORTED state (for approve/reject tests)</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>SELECT tr.id, tr.executor_login, tr.task_id, tr.report_date, tr.effort, tr.state
+FROM ttt_backend.task_report tr
+WHERE tr.state = 'REPORTED'
+AND tr.report_date &gt;= '2026-03-01'
+ORDER BY tr.report_date DESC LIMIT 20;</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Check if report period is open for target date</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>SELECT o.id as office_id, o.name, rp.start as report_period_start
+FROM ttt_backend.office o
+JOIN ttt_backend.office_period rp ON o.report_period_id = rp.id
+WHERE rp.start &lt;= CURRENT_DATE;</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Find employees with over-reported hours</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>SELECT tr.executor_login, SUM(tr.effort) as total_minutes,
+       ROUND(SUM(tr.effort) / 60.0, 1) as total_hours
+FROM ttt_backend.task_report tr
+WHERE tr.report_date = CURRENT_DATE AND tr.state != 'DELETED'
+GROUP BY tr.executor_login
+HAVING SUM(tr.effort) &gt; 480
+ORDER BY total_minutes DESC;</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>5. Data Generation Strategies</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="n"/>
+      <c r="C37" s="24" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>reportDate</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Must fall within OPEN report period. Use CURRENT_DATE or dates within current period. Format: YYYY-MM-DD.</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>effort</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>In MINUTES. Standard: 60 (1h), 480 (8h). Boundary: 1 (min), 1440 (24h — system max), 0 (expect error).</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>taskId</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Must be a valid task ID in a project the employee is assigned to. Query employee_project + task tables.</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Timestamp generation</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Use ISO format: YYYY-MM-DDTHH:mm:ss. Reports use date-only (YYYY-MM-DD).</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>6. Environment Reference</t>
+        </is>
+      </c>
+      <c r="B44" s="23" t="n"/>
+      <c r="C44" s="24" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>timemachine</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>https://ttt-timemachine.noveogroup.com</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Primary dev env — has test clock (PATCH to advance time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>qa-1</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>https://ttt-qa-1.noveogroup.com</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Secondary dev env — real clock</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>https://ttt-stage.noveogroup.com</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Production-like env — read-only testing preferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>7. API Authentication</t>
+        </is>
+      </c>
+      <c r="B50" s="23" t="n"/>
+      <c r="C50" s="24" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>How to Obtain/Use</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>JWT (user context)</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Login via CAS SSO at /login, extract TTT_JWT_TOKEN cookie. Pass as Authorization: Bearer &lt;token&gt; or Cookie header.</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Most endpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>API token</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>Set header API_SECRET_TOKEN: &lt;token_value&gt;. Value from env config file.</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>Test/sync endpoints, limited scope</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A29:C29"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="002F5496"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1034,7 +1884,7 @@
       </c>
       <c r="B1" s="19" t="inlineStr">
         <is>
-          <t>Suite: API Errors, Edge Cases &amp; Integration</t>
+          <t>Suite: Confirmation Notification Bug #3368</t>
         </is>
       </c>
     </row>
@@ -1093,82 +1943,94 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-091</t>
+          <t>TC-RPT-111</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Error code: NOT_FOUND (404) on non-existent report</t>
+          <t>By Employee tab shows over/under report notification</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Authenticated user.</t>
+          <t>Employee has over-reported or under-reported hours for approve period;
+Confirmation page open; timemachine env</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>1. PATCH /api/ttt/v1/reports/999999999
-2. Observe error response</t>
+          <t>1. Navigate to Confirmation &gt; By Employee
+2. Select an employee with over/under reported hours
+3. Check for notification banner showing hours deviation
+4. Navigate to Confirmation &gt; By Projects
+5. Select the same employee
+6. Compare notification content between both tabs</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>HTTP 404. Error code: NOT_FOUND.
-NotFoundException from InternalTaskReportService.
-Note: GET /reports/{id} returns 500 (no GET-by-ID endpoint).</t>
+          <t>Both tabs show identical over/under report notification.
+Notification displays: reported hours, norm hours, deviation.
+By Employee tab fetches statistics via employee approve period API.</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr"/>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>#3368</t>
+        </is>
+      </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>InternalTaskReportService, RestErrorHandler</t>
+          <t>Confirmation / employeeTabSagas.ts</t>
         </is>
       </c>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>GET by ID returns 500 -- must use search</t>
+          <t>Root cause was By Employee tab never calling statistics endpoint</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>TC-RPT-092</t>
+          <t>TC-RPT-112</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Error code: exception.ttt.lock (423) on lock conflict</t>
+          <t>By Employee — norm display uses normForDate with fallback</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Two concurrent users editing same report.</t>
+          <t>Employee has statistics data; some months have date-specific norm, others don't</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>1. User A: PATCH report (acquires lock)
-2. User B (within 1 min): PATCH same report
-3. Observe User B error</t>
+          <t>1. Navigate to Confirmation &gt; By Employee
+2. Select employee with date-specific norm (part-month employment)
+3. Verify notification shows normForDate value
+4. Select employee with standard full-month norm
+5. Verify notification shows general norm when normForDate is null
+6. Verify 'Monthly norm' and 'Norm as of {date}' labels displayed correctly</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>HTTP 423 Locked.
-Error code: exception.ttt.lock.
-TttLockException with lock holder details.</t>
+          <t>normForDate displayed when available.
+Fallback to general norm when normForDate is null.
+Labels 'Monthly norm' and 'Norm as of {date}' shown correctly.</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -1178,938 +2040,206 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr"/>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>#3368 / !5132</t>
+        </is>
+      </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>LockService, RestErrorHandler</t>
+          <t>Confirmation / TEmployeeStatistics</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>423 is unique to reports module</t>
+          <t>Fix: normForDate || norm fallback in saga</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-093</t>
+          <t>TC-RPT-113</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Error code: exception.ttt.security (403) on permission denied</t>
+          <t>By Employee — approve period determines notification month</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>User without REPORTS_EDIT on target task.</t>
+          <t>Office approve period is for a past month (not current month);
+Employee has overwork in both past and current month</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>1. POST /api/ttt/v1/reports/create for task without REPORT permission</t>
+          <t>1. Set office approve period to a past month (e.g., February when current is March)
+2. Ensure employee has over-reported hours in BOTH months
+3. Navigate to Confirmation &gt; By Employee
+4. Select the employee
+5. Verify notification shows deviation for APPROVE MONTH (past), not current month
+6. Navigate to Confirmation &gt; By Projects
+7. Verify SAME month shown in notification</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>HTTP 403. Error code: exception.ttt.security.
-TttSecurityException.
-Distinct from AccessDeniedException (which gives FORBIDDEN).</t>
+          <t>By Employee shows notification for approve period month, not current month.
+Both tabs show identical month context.
+When approve month &lt; current month: notification uses approvePeriod.periodStart.</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr"/>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>#3368 / !5205</t>
+        </is>
+      </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>InternalTaskReportService, RestErrorHandler</t>
+          <t>Confirmation / employeeTabSagas.ts</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>Different from vacation's exception.vacation.no.permission</t>
+          <t>Bug: By Employee showed current month; By Projects showed approve month</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>TC-RPT-094</t>
+          <t>TC-RPT-114</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Error code: CONFLICT (409) on duplicate report</t>
+          <t>By Employee — officeId resolution fallback</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Existing report for same task+date+executor.</t>
+          <t>Employee DTOs may have officeId at different paths: direct .officeId or .office.id</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>1. POST duplicate report
-2. Inspect error response</t>
+          <t>1. Navigate to Confirmation &gt; By Employee
+2. Select an employee (check that approve period loads correctly)
+3. Verify no JavaScript errors in browser console
+4. Test with employees from different offices
+5. Verify approve period fetched correctly for each office</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>HTTP 409. Error code: CONFLICT.
-AlreadyExistsException with 'existentObject' field.
-existentObject contains the existing report's ID.</t>
+          <t>Approve period loaded correctly for all employees.
+No errors from undefined officeId.
+Fallback: uses employee.officeId || employee.office.id.</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr"/>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>#3368 / !5256</t>
+        </is>
+      </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>InternalTaskReportService, RestErrorHandler</t>
+          <t>Confirmation / employeeTabSagas.ts</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>Response contains existing report reference</t>
+          <t>Different DTO shapes: some have officeId directly, others at office.id</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-095</t>
+          <t>TC-RPT-115</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Error code: FORBIDDEN (403) on FINISHED project</t>
+          <t>By Employee — approve button switches to next user correctly</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Task on FINISHED project.</t>
+          <t>Multiple employees with pending approvals; By Employee tab open</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>1. POST report for FINISHED project task
-2. Inspect error</t>
+          <t>1. Navigate to Confirmation &gt; By Employee
+2. Select first employee in list with pending approval
+3. Click Approve button
+4. Verify: a) Approval succeeds b) View switches to next employee
+5. Verify notification updates for the new employee
+6. Verify employee list refreshes with updated status</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>HTTP 403. ProjectFinishedException.
-Error code: FORBIDDEN (mapped from ProjectFinishedException).</t>
+          <t>After approve: view auto-switches to next pending employee.
+Notification refreshes with new employee's statistics.
+Employee list updates (approved employee removed from pending).
+updateEmployeesWeeksAndMonths called with employee parameter.</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr"/>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>#3368 / !5132</t>
+        </is>
+      </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>RestErrorHandler</t>
+          <t>Confirmation / employeeTabSagas.ts</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>ProjectFinishedException -&gt; 403</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-096</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Error code: BAD_REQUEST (400) with field-level details</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Invalid create request.</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>1. POST with missing required fields
-2. Inspect validation error structure</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>HTTP 400. Error code: BAD_REQUEST.
-MethodArgumentNotValidException provides field-level details.
-Each invalid field listed with violation message.</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>RestErrorHandler</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>ConstraintViolationException also maps to 400</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-097</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>ServiceException maps to 500 (inconsistent with vacation's 400)</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Trigger an internal service error.</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>1. Create scenario causing ServiceException
-2. Observe HTTP status</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>HTTP 500. ServiceException maps to INTERNAL_SERVER_ERROR in TTT.
-Inconsistency: same ServiceException maps to 400 in vacation service.
-Different RestErrorHandler implementations per service.</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr"/>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>RestErrorHandler</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>TTT: 500, Vacation: 400 -- inconsistent across services</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-098</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Effort boundary: @Min(0) on PATCH allows negative effect via 0</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Existing report.</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>1. PATCH with {effort: 0} -&gt; deletes report
-2. PATCH with {effort: -1} -&gt; validation error</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>effort=0: report deleted (valid, @Min(0)).
-effort=-1: HTTP 400 @Min(0) violation.
-Boundary at 0: deletes. Below 0: rejected.</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>Boundary</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr"/>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>TaskReportEditRequestDTO</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>Asymmetry: create @Min(1), edit @Min(0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-099</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Report with effort displayed in hours (÷60 conversion)</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Report with effort=90 minutes.</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>1. Create report with effort=90
-2. Check UI display in My Tasks
-3. Check API response</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>API: effort=90 (minutes, integer).
-UI: displays 1.5 (hours, effort/60).
-Conversion in frontend: calcEmployeeEffort() divides by 60.</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr"/>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>frontend-report-module</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>API uses minutes, UI shows hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-100</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>My Tasks page -- task add via quick search</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Employee on /report page.</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>1. Click 'Add task' search field
-2. Type task name (partial match)
-3. Select from suggestions
-4. Verify task appears in report grid</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>TaskAddContainer provides type-ahead search.
-Suggestion endpoint: GET /api/ttt/v1/tasks?search=&lt;query&gt;.
-Selected task added to employee's visible report grid.</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>frontend-report-module, TaskAddContainer</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-101</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>My Tasks page -- pin/unpin task for quick access</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Employee with tasks on /report page.</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>1. Pin a task: POST /api/ttt/v1/tasks/&lt;id&gt;/employees/&lt;login&gt;/pin
-2. Verify task appears at top of list
-3. Unpin: DELETE /api/ttt/v1/tasks/&lt;id&gt;/employees/&lt;login&gt;/pin</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>Pinned tasks appear at top of My Tasks table.
-Pin persists across sessions.
-Unpin removes from pinned list.</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr"/>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>frontend-report-module</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>Pin/unpin via POST/DELETE endpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-102</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>My Tasks page -- week switcher navigation</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Employee on /report page.</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>1. Click previous/next week arrows
-2. Observe date range update
-3. Verify reports refresh for new week</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Week navigation with left/right arrows.
-Shows Monday-Sunday range.
-Complex date math with Moment.js (tech debt -- should use date-fns).</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>frontend-report-module, WeekSwitcherContainer</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>Moment.js tech debt</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-103</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>My Tasks page -- grouped by project vs ungrouped toggle</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Employee with tasks across multiple projects.</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>1. Toggle 'Grouped by project' switch
-2. Verify table layout changes</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>Ungrouped: flat task list.
-Grouped: tasks organized under project headers.
-Toggle state persisted in Redux uiFiltersReducer.</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr"/>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>frontend-report-module, ProjectsGroupedSwitcher</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-104</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Report event system -- add/patch/delete events published</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Create, edit, delete reports.</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>1. POST /api/ttt/v1/reports/create -&gt; TaskReportAddEvent
-2. PATCH /api/ttt/v1/reports/&lt;id&gt; -&gt; TaskReportPatchEvent
-3. DELETE -&gt; TaskReportDeleteEvent (also via effort=0)</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Three event types published:
-- TaskReportAddEvent: on creation
-- TaskReportPatchEvent: on update (with before-state)
-- TaskReportDeleteEvent: on delete AND on effort=0
-Events drive: statistics cache, audit trail, notifications.</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr"/>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>TaskReportEventListener</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>Async + transactional event listener</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-105</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Accounting notifications -- send reminders to employees</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Accountant on accounting page with unconfirmed reports.</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>1. POST /api/ttt/v1/reports/send-accounting-notifications
-2. Check emails sent</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Sends reminder notifications to employees with unconfirmed hours.
-Accountant-initiated action (not scheduled).
-AUTHENTICATED_USER only (no API token).</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr"/>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>TaskReportController</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>Manual trigger by accountant</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-106</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>GET /reports/accounting -- paginated by office and date range</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Accountant JWT auth.</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>1. GET /api/ttt/v1/reports/accounting?officeId=&lt;id&gt;&amp;from=2026-03-01&amp;to=2026-03-31
-2. Verify pagination structure</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>Paginated response filtered by office and date range.
-Used by accountant confirmation view.
-JWT only -- API token returns 403.</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>TaskReportController</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-107</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Hardcoded CEO login in statistics -- ilnitsky</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Code inspection / behavior verification.</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>1. Check StatisticReportService for CEO_LOGIN constant
-2. Verify special handling for CEO login</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Hardcoded: CEO_LOGIN = 'ilnitsky'.
-CEO excluded from certain statistics calculations.
-Design issue: hardcoded login instead of role-based check.</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>StatisticReportService</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>Hardcoded CEO login -- design debt</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-108</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Daily report effort limit -- 36h (2160 minutes) warning threshold</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Employee reporting &gt;36h on a single day.</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>1. Create reports totaling &gt;2160 min on one day
-2. Check for warning generation</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Warning type: DATE_EFFORT_OVER_LIMIT generated.
-36h = 2160 minutes per day threshold.
-Warning only -- does not prevent report creation.</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Boundary</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr"/>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>TaskReportWarningController</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>Warning only, not enforcement</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-109</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>DTO response structure -- all fields verified</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Create a report and inspect full response.</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>1. POST /api/ttt/v1/reports/create
-2. Inspect response JSON structure</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Response DTO fields:
-- id (Long), state (REPORTED|APPROVED|REJECTED)
-- stateComment (null unless REJECTED)
-- effort (Long, minutes), reportDate (ISO date)
-- executorLogin, reporterLogin, approverLogin
-- periodState (OPEN|CLOSED), reportComment
-- projectState {id, name, status}
-- permissions[] (EDIT, DELETE, APPROVE subset)</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr"/>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>TaskReportDTO</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-110</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Reject response shows approverLogin derived from reject.rejector</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Report in REJECTED state.</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>1. Reject a report with known rejector
-2. GET report via search
-3. Check approverLogin field</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>API response shows approverLogin for rejected reports.
-But DB column task_report.approver is NULL.
-Value derived from reject.rejector (join query).
-Confusing: field named 'approver' but shows rejector.</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="inlineStr"/>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>InternalTaskReportService</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>Naming confusion: approverLogin shows rejector on rejected reports</t>
+          <t>Fix changed spawn to call for updateEmployeesWeeksAndMonths</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J23"/>
+  <autoFilter ref="A3:J8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
   </hyperlinks>
@@ -2124,7 +2254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2139,322 +2269,330 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>← Back to Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Feature Area</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Bug Verification</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>Test Suite</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>CRUD (Create/Update/Delete/Batch)</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B3" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C3" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D2" s="9" t="n">
+      <c r="D3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F3" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G2" s="9" t="n">
+      <c r="G3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="9" t="n">
+      <c r="H3" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>TS-RPT-CRUD</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Confirmation (Approve/Reject/Auto)</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n">
+      <c r="B4" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C4" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D4" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E4" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F4" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G3" s="11" t="n">
+      <c r="G4" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="H3" s="11" t="n">
+      <c r="H4" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>TS-RPT-Confirmation</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Period Management</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B5" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C5" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="9" t="n">
+      <c r="H5" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>TS-RPT-Periods</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Lock Management</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H6" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>TS-RPT-Locks</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Statistics &amp; Norms</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B7" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>TS-RPT-Statistics</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Permissions &amp; Security</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B8" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C8" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E8" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F8" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H8" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>TS-RPT-Permissions</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>API Errors &amp; Edge Cases</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B9" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G9" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="H9" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>TS-RPT-APIErrors</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B10" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C10" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D10" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E10" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F10" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G10" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>110</v>
       </c>
-      <c r="I9" s="14" t="n"/>
+      <c r="I10" s="14" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I9"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2467,7 +2605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2479,480 +2617,487 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>← Back to Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>Likelihood</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Mitigation / Test Focus</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Self-approval via API</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>No executor!=approver check in backend. Employees with PM role on their own projects can approve their own reports via API. UI may mask this by hiding approve button on own reports.</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Test PM approving own reports. Verify no backend check exists. Document UI vs API behavior difference.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Direct create-as-APPROVED bypasses workflow</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>POST /reports with state=APPROVED creates pre-approved report. Skips REPORTED-&gt;APPROVED state machine entirely. Initial state should be forced to REPORTED regardless of input.</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>POST with state=APPROVED. Verify report created with APPROVED state. Document bypass path.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>No upper bound on effort (25h+ accepted)</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>No @Max annotation on effort field. Reports can be created with effort=99999 minutes. Warning system exists but doesn't prevent creation. Data integrity concern.</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Create reports with extreme effort values. Verify no rejection. Check if warning threshold (36h/2160min) generates warning only.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Missing @PreAuthorize on /effort and /employee-projects</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Two GET endpoints accessible without any authentication. No @PreAuthorize annotation. Data exposed to unauthenticated callers.</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Access both endpoints without JWT or API token. Verify data returned without authentication.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Lock bypass via batch PUT</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Batch PUT /v1/reports skips locking mechanism. Concurrent batch operations can cause data races. Individual PATCH properly acquires locks.</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Concurrent batch PUT operations on same tasks. Verify no lock conflict raised (by design).</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Auto-reject never triggered on test environments</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Auto-reject feature (approve period close) has never been triggered. No reject records with description='auto.reject.state' exist. Feature functionally untested in practice.</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Manually advance approve period to trigger auto-reject. Verify reports rejected, emails sent, warnings displayed.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Missing first-day-of-month validation on approve period</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Report period validates getDayOfMonth()!=1 but approve period does NOT. Any day of month accepted for approve period. Asymmetric validation between the two period types.</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>PATCH approve period with mid-month date. Verify accepted (bug). Compare with report period rejection.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>NPE on empty PATCH body for approve period</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>PATCH /periods/approve with {} body causes NullPointerException. start field is null, getMonth() fails. Missing null check on request body.</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Send empty PATCH body. Verify 500 NPE response. Document missing null validation.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Stack trace leakage in period error responses</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Invalid date format in PATCH body returns full Java stack trace. Exposes internal class names, package structure, Spring version. Information disclosure vulnerability.</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>Send invalid date format. Verify stack trace in response.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Race condition in statistic_report updates</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>No pessimistic locking between RabbitMQ handler and @Async task report event. Concurrent updates to statistic_report can produce incorrect cached values. Self-heals on nightly sync but incorrect during the day.</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Trigger concurrent report + vacation change. Check statistic_report for inconsistency.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Cross-employee reporting without role check</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Any authenticated user can POST reports with any executorLogin. Intended for manager-reports-on-behalf but no PM role verification. Data attribution concern.</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Employee A reports for Employee B. Verify no role check prevents this.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Reject history not preserved</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Re-reporting (effort change) on REJECTED report deletes the Reject record. No rejection history maintained. Cannot audit how many times report was rejected. approverLogin cleared on re-report.</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Reject report, then re-report. Verify reject record deleted from DB.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>ServiceException: 500 in TTT vs 400 in vacation</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Same ServiceException class maps to HTTP 500 in TTT service but HTTP 400 in vacation service. Different RestErrorHandler implementations. Inconsistent error contract across services.</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>Trigger ServiceException in both services. Compare HTTP status codes.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Future date accepted without restriction</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>No forward-date validation on reportDate. Reports can be created for dates far in the future. Only backward restriction (report period) exists.</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Create report with date 6+ months in future. Verify accepted.</t>
         </is>
@@ -2960,6 +3105,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F15"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4135,1129 +4283,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>&lt;- Back to Plan</t>
-        </is>
-      </c>
-      <c r="B1" s="19" t="inlineStr">
-        <is>
-          <t>Suite: Confirmation (Approval/Rejection) Flow</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Test ID</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>Requirement Ref</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>Module/Component</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-021</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Approve report -- REPORTED -&gt; APPROVED transition</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Report in REPORTED state. User has REPORTS_APPROVE on task.
-reportDate &gt;= approve period start.</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>1. PATCH /api/ttt/v1/reports/&lt;id&gt;
-2. Body: {state: 'APPROVED'}
-3. Verify state and approverLogin</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>state=APPROVED. approverLogin set to current user.
-stateComment cleared. Rejection record deleted if existed.
-Audit trail updated.</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>REQ-reports Confirmation</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>InternalTaskReportService</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-022</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Reject report -- REPORTED -&gt; REJECTED with comment</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Report in REPORTED state. User has REPORTS_APPROVE.</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>1. PATCH /api/ttt/v1/reports/&lt;id&gt;
-2. Body: {state: 'REJECTED', stateComment: 'Wrong project'}
-3. Verify state, stateComment
-4. Check reject table in DB</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>state=REJECTED. stateComment='Wrong project'.
-Reject record created in ttt_backend.reject table:
-rejector, description='Wrong project', executor_notified=false.
-Notification sent within 5 min by sendRejectNotifications scheduler.</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>REQ-reports Confirmation</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>InternalTaskReportService</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>Reject creates DB record in reject table</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-023</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Reject report -- stateComment is optional (API allows null)</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Report in REPORTED state.</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>1. PATCH with {state: 'REJECTED'} (no stateComment)
-2. Verify rejection succeeds</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Rejection succeeds without comment.
-Reject record created with NULL description.
-Note: UI requires comment (textarea), but API doesn't enforce.</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>InternalTaskReportService</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>Frontend requires comment, backend doesn't</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-024</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Re-report after rejection -- effort change resets to REPORTED</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Report in REJECTED state with reject record.</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>1. PATCH with {effort: 90} (changed effort)
-2. Verify state and reject record</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>State reset from REJECTED to REPORTED.
-Reject record DELETED from ttt_backend.reject table (no history preserved).
-approverLogin cleared. Employee can re-report after rejection.</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>REQ-reports Re-report</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>InternalTaskReportService</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>Reject record deleted -- no rejection history kept</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-025</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>BUG: Self-approval -- no executor != approver check</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Employee's own report in REPORTED state.
-Employee also has REPORTS_APPROVE (PM role on own project).</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>1. Login as employee who is PM on their own project
-2. PATCH own report with {state: 'APPROVED'}
-3. Verify approval succeeds</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>BUG: Self-approval succeeds.
-approverLogin = executorLogin.
-No business rule prevents approving own reports.
-Should require executor != approver.</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>Bug verification</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>BUG-REPORT-2</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>InternalTaskReportService</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>No executor!=approver check anywhere in the chain</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-026</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Approve blocked for PROJECT_MANAGER type projects</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Report on a project with type=PROJECT_MANAGER.
-User has REPORTS_APPROVE.</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>1. PATCH with {state: 'APPROVED'} for project type PROJECT_MANAGER
-2. Expect rejection or skip</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Approval blocked for PROJECT_MANAGER type projects.
-Business rule: these projects cannot be approved.
-State remains REPORTED.</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>InternalTaskReportService</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>PROJECT_MANAGER type special handling</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-027</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Approve blocked if reportDate &lt; approve period start</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Report with reportDate before approve period start.
-User has REPORTS_APPROVE.</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>1. GET approve period start for office
-2. PATCH report with reportDate before that start
-3. Body: {state: 'APPROVED'}</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>Approval blocked. reportDate must be &gt;= approve period start.
-Only affects approval, not rejection.
-periodState shows CLOSED in response.</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>REQ-reports Periods</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>InternalTaskReportService</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-028</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Confirmation page -- By employees view</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Logged in as PM with REPORTS_APPROVE. Navigate to /approve.</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>1. Open Confirmation page
-2. Select 'By employees' tab
-3. Observe layout: employee rows, week tabs, task columns</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Week navigation: 6 week tabs. Orange dot on tabs with pending items.
-Employee rows expand to show tasks with daily effort cells.
-Approve button per task (all days in week).
-Bulk approve header button available.</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>REQ-reports Confirmation UI</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>frontend-approve-module</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-029</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Confirmation page -- By projects view</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>PM with multiple projects.</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>1. Switch to 'By projects' tab
-2. Observe grouping</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Projects listed with employees grouped under each.
-N+1 API pattern: ~5N requests for N employees.
-Same approve/reject controls as By employees view.</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>REQ-reports Confirmation UI</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>frontend-approve-module</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>Known performance issue: N+1 API pattern</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-030</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Confirmation page -- reject with comment via tooltip</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Report in REPORTED state. PM on Confirmation page.</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>1. Click reject icon on a task row
-2. Observe tooltip with textarea
-3. Enter rejection comment
-4. Click reject button</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Tooltip opens with textarea for rejection comment.
-Comment required in UI (submit button disabled without text).
-PATCH sent with state=REJECTED, stateComment=&lt;entered text&gt;.
-Report shows as rejected in the table.</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>REQ-reports Confirmation UI</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>frontend-approve-module</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>UI requires comment; API makes it optional</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-031</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>BUG: 'employee is undefined' TypeError after approve click</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>PM on Confirmation page. Approve a task.</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>1. Open browser console (F12)
-2. Click Approve on a task
-3. Check console for errors</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>BUG: 'employee is undefined' TypeError in console.
-Non-blocking race condition.
-Approval still succeeds, but console error logged.
-Likely timing issue in React state update.</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>Bug verification</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>BUG-CONFIRM-1</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>frontend-approve-module</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>Non-blocking race condition in React</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-032</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Confirmation page -- 'With approved hours' toggle</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>PM with approved and unapproved reports in same week.</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>1. Toggle 'With approved hours' filter
-2. Observe table changes</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Toggle OFF (default): only REPORTED state visible.
-Toggle ON: both REPORTED and APPROVED visible.
-Affects which reports are shown in the grid.</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>frontend-approve-module</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-033</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Confirmation page -- 'Of other projects' checkbox</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>PM with reports on projects they don't manage.</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>1. Check 'Of other projects' checkbox
-2. Observe additional rows</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>Shows reports on projects where user has VIEW but not APPROVE.
-Read-only — no approve/reject buttons on these rows.</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr"/>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>frontend-approve-module</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-034</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Auto-reject on approve period close</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Reports in REPORTED state. Accountant advances approve period.</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>1. Identify reports in REPORTED state within current approve period
-2. PATCH /&lt;officeId&gt;/periods/approve to advance
-3. Verify reports now REJECTED
-4. Check reject table for auto.reject.state</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>All REPORTED reports in closed period auto-rejected.
-Single shared Reject record with description='auto.reject.state'.
-Notification emails sent to affected employees.
-PeriodChangedEvent published.</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>REQ-reports Auto-reject</t>
-        </is>
-      </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>TaskReportServiceImpl, InternalTaskReportService</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>Distinguish auto from manual: reject.description='auto.reject.state'</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-035</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Auto-reject warnings on My Tasks page</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Employee with auto-rejected reports.</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>1. Navigate to /report (My Tasks)
-2. Check for auto-reject notification banners at top</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>AutoRejectedReportsContainer shows error notifications:
-'Unconfirmed hours for task {taskName} were automatically rejected upon month closure'
-'Go to the report page' link navigates to rejection week.
-Close button hides via localStorage (hiddenAutoRejectWarnings).</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr"/>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>frontend-report-module, AutoRejectedReportsContainer</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>Displays on /report page, NOT /approve page</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-036</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Auto-reject -- no data exists on testing environments</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Timemachine/qa-1/stage environments.</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>1. SELECT * FROM ttt_backend.reject WHERE description = 'auto.reject.state'
-2. GET /api/ttt/v1/task-auto-reject-warnings</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>No auto-reject records exist on any testing environment.
-Feature never triggered.
-Warning endpoint returns empty array.
-Must trigger manually to test.</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>TaskReportAutoRejectController</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>Feature untested in practice</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-037</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Reject notification -- sent within 5 minutes by scheduler</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Reject a report. Wait for notification dispatch.</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>1. PATCH report to state=REJECTED
-2. Verify reject.executor_notified=false in DB
-3. Trigger sendRejectNotifications scheduler (or wait 5 min)
-4. Check email via GET /api/email/v1/emails</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Reject record created with executor_notified=false.
-Scheduler sendRejectNotifications runs every 5 min.
-Sends APPROVE_REJECT email template to executor.
-After send: executor_notified=true.</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>REQ-reports Notifications</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>sendRejectNotifications scheduler</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>Schedule: every 5 minutes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>TC-RPT-038</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>BUG: Reject email not reliably sent (timing/date filtering)</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Reject a report and trigger notification scheduler.</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>1. Reject a report via PATCH
-2. Trigger send-reject-notifications
-3. Check if email sent via GET /api/email/v1/emails</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>BUG: Reject email sometimes not sent.
-Suspected timing/date filtering issue in scheduler query.
-executor_notified may not update correctly.</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Bug verification</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>BUG-CONFIRM-2</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>sendRejectNotifications</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>Intermittent -- timing-dependent</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>TC-RPT-039</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>BUG: APPROVE permission appears/disappears between PATCH and GET</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Manager approves a report.</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>1. PATCH report to APPROVED (returns permissions array)
-2. Immediately GET same report
-3. Compare permissions arrays</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>BUG: APPROVE permission present in PATCH response
-but absent from subsequent GET response (or vice versa).
-Permission calculation race condition.</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>Bug verification</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>BUG-CONFIRM-3</t>
-        </is>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>TaskReportPermissionType</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t>Timing-dependent permission inconsistency</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:J22"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="002F5496"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6278,7 +5303,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002F5496"/>
@@ -6722,6 +5747,807 @@
     </row>
   </sheetData>
   <autoFilter ref="A3:J10"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5496"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>Suite: Statistics, Norms &amp; Notifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>Requirement Ref</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>Module/Component</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>TC-RPT-065</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Personal norm calculation -- excludes time-offs</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Employee with 5 vacation days in March 2026.
+Office calendar has 22 working days in March.</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>1. GET /api/ttt/v1/reports/summary for March
+2. Verify norm = (22 - 5) * 8 * 60 minutes
+3. Cross-reference with DB: statistic_report table</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>personalNorm = max(0, calendarNorm - offHours).
+Off hours include: vacations + sick leaves + day-offs + maternity.
+Overlapping off-periods merged before calculation.
+Result in minutes.</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>REQ-reports Norms</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>NormService</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>Norm = (workDays - timeOffDays) * 8h * 60min</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>TC-RPT-066</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Budget norm -- excludes admin vacations from off-periods</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Employee with both paid vacation (5 days) and admin/unpaid vacation (3 days).</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>1. GET summary or statistic_report
+2. Compare personal vs budget norm</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>budgetNorm = calendarNorm - (offHours EXCLUDING admin vacations).
+Employee on unpaid leave still counted in budget.
+Display (#3381): '{individual} ({budget})' when admin vacation exists.</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>REQ-reports Norms #3381</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>NormService</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>Budget includes admin vacation days as working</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>TC-RPT-067</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Norm display format -- with/without admin vacation</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Employee A: has admin vacation. Employee B: no admin vacation.</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>1. Check norm display for Employee A
+2. Check norm display for Employee B</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Employee A: '{individual} ({budget})' format (two values).
+Employee B: just '{budget}' (single value).
+Format switches based on presence of admin vacation.</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>REQ-reports #3381</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>frontend-report-module</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>#3381 display format</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>TC-RPT-068</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Forgotten report threshold -- 90% of personal norm</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Employee with personalNorm=9600 min (20 days * 8h).
+Reported effort = 8500 min (88.5% of norm).</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>1. Check if employee receives forgotten notification
+2. Trigger sendReportsForgottenNotifications</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Threshold: 90% of personalNorm = 8640 min.
+8500 &lt; 8640 → employee is under-reported.
+Forgotten report notification sent.
+Schedule: Mon/Fri 16:00.</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>REQ-reports Notifications</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>sendReportsForgottenNotifications</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>Threshold: 90% of personal norm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>TC-RPT-069</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Statistic report table -- nightly sync updates cache</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Timemachine environment.</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>1. SELECT * FROM ttt_backend.statistic_report WHERE employee_login='&lt;login&gt;' AND report_date='2026-03-01'
+2. Verify fields: reported_effort, month_norm, budget_norm</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Pre-computed cache in ttt_backend.statistic_report.
+Nightly sync at 4:00 AM updates current + previous month.
+Three update paths: nightly cron, task report @Async, RabbitMQ.</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>StatisticReportScheduler</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>3 update paths can cause race conditions (BUG-STATS-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>TC-RPT-070</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Deviation formula and ExcessStatus enum</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Employee with reported=9000 min, budgetNorm=8800 min.</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>1. Calculate: (9000-8800)/8800 * 100 = 2.27%
+2. Verify ExcessStatus in API response</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>excess = (reported - budgetNorm) / budgetNorm * 100%.
+ExcessStatus: HIGH (&gt;0%), LOW (&lt;0%), NEUTRAL (==0%), NA (budgetNorm=0).
+Display: integer %. Exception: (-1,+1) range shows 1 decimal.
+NA displays as '+N/A%' and sorts to top.</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>StatisticReportService</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>Special display for values near zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>TC-RPT-071</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Over/under-reporting banner on Confirmation page</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>PM with over-reported employee in current month.</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>1. Navigate to /approve (Confirmation page)
+2. Observe banner notification</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Non-dismissible banner visible to ADMIN, PM, SPM.
+Triggers: over-reporting today (current month) OR at month end.
+Employee names: red=over, purple=under.
+Clock icon tooltip: deviation %, month, DM, projects with PM names.</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>REQ-reports Over-reporting</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>frontend-approve-module</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>Non-dismissible -- always visible when condition exists</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>TC-RPT-072</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>GET /over-reported endpoint</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Authenticated user with REPORTS_VIEW.</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>1. GET /api/ttt/v1/reports/over-reported</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Returns employees with over-reported hours.
+Legacy endpoint with N+1 pattern, superseded by statistic_report cache.
+Still functional but inefficient.</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr"/>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>TaskReportController</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>Legacy N+1 endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>TC-RPT-073</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Employee Reports page access by role</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Users with different roles.</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>1. ADMIN: access /employee-reports -&gt; sees all employees
+2. OFFICE_DIRECTOR: sees their office only
+3. DEPARTMENT_MANAGER: sees subordinates only
+4. EMPLOYEE: cannot access</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>ADMIN, CHIEF_ACCOUNTANT: all employees.
+OFFICE_DIRECTOR, ACCOUNTANT: their office.
+DEPARTMENT_MANAGER, TECH_LEAD: subordinates.
+EMPLOYEE: no access (no route guard).</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>REQ-reports Statistics view</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>frontend-report-module</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>Role-scoped data access</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>TC-RPT-074</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>BUG: Race condition between MQ and task report event paths</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Concurrent statistic_report update from two sources.</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>1. Submit report (triggers @Async task report event)
+2. Simultaneously process RabbitMQ vacation change
+3. Check statistic_report for inconsistency</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>BUG: No pessimistic locking between MQ handler and task report event.
+Both paths update statistic_report.reported_effort.
+Race condition can produce incorrect cached values.
+Inconsistency resolves on next nightly sync.</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>Bug verification</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>BUG-STATS-1</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>StatisticReportService</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>Self-healing via nightly sync, but incorrect during day</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>TC-RPT-075</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Statistic report -- 2-month sync window only</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Historical data older than 2 months.</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>1. Check statistic_report for dates 3+ months ago
+2. Verify nightly sync only covers current + previous month</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Nightly sync covers current + previous month only.
+No historical back-fill mechanism.
+Older months may have stale data if never manually refreshed.</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>StatisticReportScheduler</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>Design limitation: no historical sync</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>TC-RPT-076</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Reports changed notification -- manager reported on behalf</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Manager reports hours for employee on employee's task.</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>1. Manager: POST /api/ttt/v1/reports/create with executorLogin=employee
+2. Trigger sendReportsChangedNotifications (daily 07:50)
+3. Check email</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Notification sent to employee: manager reported on their behalf.
+Template shows: task name, date, effort, reporter name.
+Schedule: daily at 07:50.</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>REQ-reports Notifications</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>sendReportsChangedNotifications</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>Triggered when reporterLogin != executorLogin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>TC-RPT-077</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Forgotten report delayed notification</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Employee still under-reported after initial notification.</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>1. Trigger sendReportsForgottenDelayedNotifications (daily 16:30)</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Retry notification for employees who received initial forgotten notification
+but still haven't reached 90% threshold.
+Schedule: daily at 16:30 (30 min after initial batch).</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr"/>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>sendReportsForgottenDelayedNotifications</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>Retry mechanism for forgotten reports</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
   </hyperlinks>
@@ -6759,7 +6585,7 @@
       </c>
       <c r="B1" s="19" t="inlineStr">
         <is>
-          <t>Suite: Statistics, Norms &amp; Notifications</t>
+          <t>Suite: Permissions, Security &amp; Access Control</t>
         </is>
       </c>
     </row>
@@ -6818,38 +6644,37 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-065</t>
+          <t>TC-RPT-078</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Personal norm calculation -- excludes time-offs</t>
+          <t>REPORTS_VIEW -- search and aggregation endpoints</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Employee with 5 vacation days in March 2026.
-Office calendar has 22 working days in March.</t>
+          <t>User with REPORTS_VIEW permission (any authenticated user on project).</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>1. GET /api/ttt/v1/reports/summary for March
-2. Verify norm = (22 - 5) * 8 * 60 minutes
-3. Cross-reference with DB: statistic_report table</t>
+          <t>1. GET /api/ttt/v1/reports?taskId=&lt;id&gt;
+2. GET /api/ttt/v1/reports/total
+3. GET /api/ttt/v1/reports/summary
+4. GET /api/ttt/v1/reports/over-reported</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>personalNorm = max(0, calendarNorm - offHours).
-Off hours include: vacations + sick leaves + day-offs + maternity.
-Overlapping off-periods merged before calculation.
-Result in minutes.</t>
+          <t>All return 200 with data.
+REPORTS_VIEW grants read access to report data.
+Includes total, summary, and over-reported endpoints.</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
@@ -6857,49 +6682,42 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>REQ-reports Norms</t>
-        </is>
-      </c>
+      <c r="H4" s="9" t="inlineStr"/>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>NormService</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>Norm = (workDays - timeOffDays) * 8h * 60min</t>
-        </is>
-      </c>
+          <t>TaskReportController</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>TC-RPT-066</t>
+          <t>TC-RPT-079</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Budget norm -- excludes admin vacations from off-periods</t>
+          <t>REPORTS_EDIT -- create, batch create, PATCH effort, delete</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Employee with both paid vacation (5 days) and admin/unpaid vacation (3 days).</t>
+          <t>User with REPORTS_EDIT (has REPORT TaskPermissionType on task).</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>1. GET summary or statistic_report
-2. Compare personal vs budget norm</t>
+          <t>1. POST /api/ttt/v1/reports/create
+2. PUT /api/ttt/v1/reports (batch)
+3. PATCH /api/ttt/v1/reports/&lt;id&gt; with {effort: 120}
+4. DELETE /api/ttt/v1/reports with {ids: [&lt;id&gt;]}</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>budgetNorm = calendarNorm - (offHours EXCLUDING admin vacations).
-Employee on unpaid leave still counted in budget.
-Display (#3381): '{individual} ({budget})' when admin vacation exists.</t>
+          <t>All succeed. REPORTS_EDIT grants full CRUD.
+EDIT condition: reportDate &gt;= report period start AND project not FINISHED.</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -6912,54 +6730,51 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>REQ-reports Norms #3381</t>
-        </is>
-      </c>
+      <c r="H5" s="11" t="inlineStr"/>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>NormService</t>
+          <t>TaskReportController, TaskReportPermissionType</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>Budget includes admin vacation days as working</t>
+          <t>EDIT = REPORT permission + date in period + project active</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-067</t>
+          <t>TC-RPT-080</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Norm display format -- with/without admin vacation</t>
+          <t>REPORTS_APPROVE -- state change to APPROVED/REJECTED</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Employee A: has admin vacation. Employee B: no admin vacation.</t>
+          <t>User with REPORTS_APPROVE (PM/SPM/ADMIN on task's project).</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>1. Check norm display for Employee A
-2. Check norm display for Employee B</t>
+          <t>1. PATCH /api/ttt/v1/reports/&lt;id&gt; with {state: 'APPROVED'}
+2. PATCH another with {state: 'REJECTED'}
+3. Verify approverLogin set</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Employee A: '{individual} ({budget})' format (two values).
-Employee B: just '{budget}' (single value).
-Format switches based on presence of admin vacation.</t>
+          <t>Both succeed. REPORTS_APPROVE grants state change rights.
+APPROVE condition: has APPROVE TaskPermissionType + reportDate &gt;= approve period.
+approverLogin set to current user on approve.</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -6967,51 +6782,44 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>REQ-reports #3381</t>
-        </is>
-      </c>
+      <c r="H6" s="9" t="inlineStr"/>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>frontend-report-module</t>
+          <t>TaskReportPermissionType, InternalTaskReportService</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>#3381 display format</t>
+          <t>APPROVE = APPROVE permission + date in approve period</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>TC-RPT-068</t>
+          <t>TC-RPT-081</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Forgotten report threshold -- 90% of personal norm</t>
+          <t>User without REPORTS_EDIT cannot create reports</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Employee with personalNorm=9600 min (20 days * 8h).
-Reported effort = 8500 min (88.5% of norm).</t>
+          <t>User with REPORTS_VIEW only (no REPORT TaskPermissionType on task).</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>1. Check if employee receives forgotten notification
-2. Trigger sendReportsForgottenNotifications</t>
+          <t>1. POST /api/ttt/v1/reports/create for a task where user has VIEW only</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Threshold: 90% of personalNorm = 8640 min.
-8500 &lt; 8640 → employee is under-reported.
-Forgotten report notification sent.
-Schedule: Mon/Fri 16:00.</t>
+          <t>HTTP 403. TttSecurityException.
+Error code: exception.ttt.security.
+REPORTS_EDIT requires REPORT permission on the specific task.</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -7021,109 +6829,100 @@
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>REQ-reports Notifications</t>
-        </is>
-      </c>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr"/>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>sendReportsForgottenNotifications</t>
+          <t>InternalTaskReportService</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>Threshold: 90% of personal norm</t>
+          <t>Per-task permission check</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-069</t>
+          <t>TC-RPT-082</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Statistic report table -- nightly sync updates cache</t>
+          <t>User without REPORTS_APPROVE cannot change state</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Timemachine environment.</t>
+          <t>Regular employee (no PM role on project).</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>1. SELECT * FROM ttt_backend.statistic_report WHERE employee_login='&lt;login&gt;' AND report_date='2026-03-01'
-2. Verify fields: reported_effort, month_norm, budget_norm</t>
+          <t>1. PATCH own report with {state: 'APPROVED'}
+2. Expect error</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Pre-computed cache in ttt_backend.statistic_report.
-Nightly sync at 4:00 AM updates current + previous month.
-Three update paths: nightly cron, task report @Async, RabbitMQ.</t>
+          <t>HTTP 403. Requires APPROVE TaskPermissionType.
+Only PM, Senior PM, ADMIN on the project can approve.</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr"/>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>StatisticReportScheduler</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>3 update paths can cause race conditions (BUG-STATS-1)</t>
-        </is>
-      </c>
+          <t>InternalTaskReportService</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>TC-RPT-070</t>
+          <t>TC-RPT-083</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Deviation formula and ExcessStatus enum</t>
+          <t>EDIT permission lost when report period closes</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Employee with reported=9000 min, budgetNorm=8800 min.</t>
+          <t>Report with reportDate=2026-02-15. Report period advanced to 2026-03-01.</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>1. Calculate: (9000-8800)/8800 * 100 = 2.27%
-2. Verify ExcessStatus in API response</t>
+          <t>1. GET report -- check permissions array
+2. PATCH report with {effort: 120}</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>excess = (reported - budgetNorm) / budgetNorm * 100%.
-ExcessStatus: HIGH (&gt;0%), LOW (&lt;0%), NEUTRAL (==0%), NA (budgetNorm=0).
-Display: integer %. Exception: (-1,+1) range shows 1 decimal.
-NA displays as '+N/A%' and sorts to top.</t>
+          <t>permissions array: EDIT absent.
+PATCH returns 403 or permission denied.
+periodState=CLOSED in response.
+EDIT requires reportDate &gt;= report period start.</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -7134,43 +6933,41 @@
       <c r="H9" s="11" t="inlineStr"/>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>StatisticReportService</t>
+          <t>TaskReportPermissionType</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>Special display for values near zero</t>
+          <t>Period closure removes EDIT/DELETE permissions</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-071</t>
+          <t>TC-RPT-084</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Over/under-reporting banner on Confirmation page</t>
+          <t>APPROVE permission lost when approve period closes</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>PM with over-reported employee in current month.</t>
+          <t>Report with reportDate=2026-01-15. Approve period advanced to 2026-02-01.</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>1. Navigate to /approve (Confirmation page)
-2. Observe banner notification</t>
+          <t>1. PATCH with {state: 'APPROVED'}
+2. Expect error</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Non-dismissible banner visible to ADMIN, PM, SPM.
-Triggers: over-reporting today (current month) OR at month end.
-Employee names: red=over, purple=under.
-Clock icon tooltip: deviation %, month, DM, projects with PM names.</t>
+          <t>APPROVE permission not granted for reports before approve period.
+Must be: reportDate &gt;= approve period start.</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -7183,61 +6980,58 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>REQ-reports Over-reporting</t>
-        </is>
-      </c>
+      <c r="H10" s="9" t="inlineStr"/>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>frontend-approve-module</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>Non-dismissible -- always visible when condition exists</t>
-        </is>
-      </c>
+          <t>TaskReportPermissionType</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>TC-RPT-072</t>
+          <t>TC-RPT-085</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>GET /over-reported endpoint</t>
+          <t>BUG: /effort endpoint missing @PreAuthorize</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Authenticated user with REPORTS_VIEW.</t>
+          <t>Unauthenticated or API token request.</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>1. GET /api/ttt/v1/reports/over-reported</t>
+          <t>1. GET /api/ttt/v1/reports/effort without JWT
+2. Observe response</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Returns employees with over-reported hours.
-Legacy endpoint with N+1 pattern, superseded by statistic_report cache.
-Still functional but inefficient.</t>
+          <t>BUG: Endpoint accessible without authentication.
+No @PreAuthorize annotation on /effort endpoint.
+Should require AUTHENTICATED_USER at minimum.</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr"/>
+          <t>Bug verification</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>BUG-REPORT-6</t>
+        </is>
+      </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
           <t>TaskReportController</t>
@@ -7245,204 +7039,198 @@
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>Legacy N+1 endpoint</t>
+          <t>Missing @PreAuthorize on 2 endpoints</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-073</t>
+          <t>TC-RPT-086</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Employee Reports page access by role</t>
+          <t>BUG: /employee-projects endpoint missing @PreAuthorize</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Users with different roles.</t>
+          <t>Unauthenticated request.</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>1. ADMIN: access /employee-reports -&gt; sees all employees
-2. OFFICE_DIRECTOR: sees their office only
-3. DEPARTMENT_MANAGER: sees subordinates only
-4. EMPLOYEE: cannot access</t>
+          <t>1. GET /api/ttt/v1/reports/employee-projects without JWT
+2. Observe response</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>ADMIN, CHIEF_ACCOUNTANT: all employees.
-OFFICE_DIRECTOR, ACCOUNTANT: their office.
-DEPARTMENT_MANAGER, TECH_LEAD: subordinates.
-EMPLOYEE: no access (no route guard).</t>
+          <t>BUG: Accessible without authentication.
+Same issue as /effort -- missing @PreAuthorize.
+Both endpoints return data without auth check.</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Bug verification</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>REQ-reports Statistics view</t>
+          <t>BUG-REPORT-6</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>frontend-report-module</t>
+          <t>TaskReportController</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>Role-scoped data access</t>
+          <t>Same bug as TC-RPT-085</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>TC-RPT-074</t>
+          <t>TC-RPT-087</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>BUG: Race condition between MQ and task report event paths</t>
+          <t>Accounting endpoints -- AUTHENTICATED_USER only</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Concurrent statistic_report update from two sources.</t>
+          <t>1. JWT authenticated user
+2. API token with permissions</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>1. Submit report (triggers @Async task report event)
-2. Simultaneously process RabbitMQ vacation change
-3. Check statistic_report for inconsistency</t>
+          <t>1. GET /api/ttt/v1/reports/accounting with JWT -&gt; verify access
+2. POST /api/ttt/v1/reports/send-accounting-notifications with JWT
+3. Same endpoints with API_SECRET_TOKEN header</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>BUG: No pessimistic locking between MQ handler and task report event.
-Both paths update statistic_report.reported_effort.
-Race condition can produce incorrect cached values.
-Inconsistency resolves on next nightly sync.</t>
+          <t>JWT: both endpoints accessible.
+API token: both return 403.
+Accounting endpoints require AUTHENTICATED_USER (JWT only).</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>Bug verification</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>BUG-STATS-1</t>
-        </is>
-      </c>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr"/>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>StatisticReportService</t>
+          <t>TaskReportController</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>Self-healing via nightly sync, but incorrect during day</t>
+          <t>No API token access to accounting endpoints</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-075</t>
+          <t>TC-RPT-088</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Statistic report -- 2-month sync window only</t>
+          <t>Warning endpoints -- AUTHENTICATED_USER only</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Historical data older than 2 months.</t>
+          <t>JWT vs API token access.</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>1. Check statistic_report for dates 3+ months ago
-2. Verify nightly sync only covers current + previous month</t>
+          <t>1. GET /api/ttt/v1/task-report-warnings with JWT
+2. GET /api/ttt/v1/task-auto-reject-warnings with JWT
+3. Same with API_SECRET_TOKEN</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Nightly sync covers current + previous month only.
-No historical back-fill mechanism.
-Older months may have stale data if never manually refreshed.</t>
+          <t>JWT: accessible. API token: 403.
+Warning endpoints require AUTHENTICATED_USER.
+Auto-reject controller returns BO directly (no DTO -- design issue).</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>StatisticReportScheduler</t>
+          <t>TaskReportWarningController, TaskReportAutoRejectController</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>Design limitation: no historical sync</t>
+          <t>Auto-reject returns BO instead of DTO (BO leak)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>TC-RPT-076</t>
+          <t>TC-RPT-089</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Reports changed notification -- manager reported on behalf</t>
+          <t>Permission calculation flow -- per-task, per-report</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Manager reports hours for employee on employee's task.</t>
+          <t>User with PM role on Project A, employee on Project B.</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>1. Manager: POST /api/ttt/v1/reports/create with executorLogin=employee
-2. Trigger sendReportsChangedNotifications (daily 07:50)
-3. Check email</t>
+          <t>1. GET reports for tasks on Project A
+2. GET reports for tasks on Project B
+3. Compare permissions arrays</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Notification sent to employee: manager reported on their behalf.
-Template shows: task name, date, effort, reporter name.
-Schedule: daily at 07:50.</t>
+          <t>Project A reports: permissions include EDIT, DELETE, APPROVE.
+Project B reports: permissions include EDIT, DELETE only.
+Permissions calculated: group by executor → by task → per report.</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -7455,48 +7243,46 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>REQ-reports Notifications</t>
-        </is>
-      </c>
+      <c r="H15" s="11" t="inlineStr"/>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>sendReportsChangedNotifications</t>
+          <t>TaskReportPermissionType</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>Triggered when reporterLogin != executorLogin</t>
+          <t>Per-task permission, not global</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-077</t>
+          <t>TC-RPT-090</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Forgotten report delayed notification</t>
+          <t>Auth polling -- excessive /authentication/check calls</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Employee still under-reported after initial notification.</t>
+          <t>Open Confirmation page in browser with network monitor.</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>1. Trigger sendReportsForgottenDelayedNotifications (daily 16:30)</t>
+          <t>1. Navigate to /approve
+2. Monitor network tab for 60 seconds
+3. Count GET /v1/authentication/check calls</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Retry notification for employees who received initial forgotten notification
-but still haven't reached 90% threshold.
-Schedule: daily at 16:30 (30 min after initial batch).</t>
+          <t>50+ GET /v1/authentication/check calls per session.
+Excessive auth polling pattern.
+Performance concern but functionally harmless.</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
@@ -7512,12 +7298,12 @@
       <c r="H16" s="9" t="inlineStr"/>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>sendReportsForgottenDelayedNotifications</t>
+          <t>frontend-approve-module</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>Retry mechanism for forgotten reports</t>
+          <t>Performance: excessive auth polling</t>
         </is>
       </c>
     </row>
@@ -7537,7 +7323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7560,7 +7346,7 @@
       </c>
       <c r="B1" s="19" t="inlineStr">
         <is>
-          <t>Suite: Permissions, Security &amp; Access Control</t>
+          <t>Suite: API Errors, Edge Cases &amp; Integration</t>
         </is>
       </c>
     </row>
@@ -7619,80 +7405,82 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-078</t>
+          <t>TC-RPT-091</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>REPORTS_VIEW -- search and aggregation endpoints</t>
+          <t>Error code: NOT_FOUND (404) on non-existent report</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>User with REPORTS_VIEW permission (any authenticated user on project).</t>
+          <t>Authenticated user.</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>1. GET /api/ttt/v1/reports?taskId=&lt;id&gt;
-2. GET /api/ttt/v1/reports/total
-3. GET /api/ttt/v1/reports/summary
-4. GET /api/ttt/v1/reports/over-reported</t>
+          <t>1. PATCH /api/ttt/v1/reports/999999999
+2. Observe error response</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>All return 200 with data.
-REPORTS_VIEW grants read access to report data.
-Includes total, summary, and over-reported endpoints.</t>
+          <t>HTTP 404. Error code: NOT_FOUND.
+NotFoundException from InternalTaskReportService.
+Note: GET /reports/{id} returns 500 (no GET-by-ID endpoint).</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="H4" s="9" t="inlineStr"/>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>TaskReportController</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr"/>
+          <t>InternalTaskReportService, RestErrorHandler</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>GET by ID returns 500 -- must use search</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>TC-RPT-079</t>
+          <t>TC-RPT-092</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>REPORTS_EDIT -- create, batch create, PATCH effort, delete</t>
+          <t>Error code: exception.ttt.lock (423) on lock conflict</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>User with REPORTS_EDIT (has REPORT TaskPermissionType on task).</t>
+          <t>Two concurrent users editing same report.</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>1. POST /api/ttt/v1/reports/create
-2. PUT /api/ttt/v1/reports (batch)
-3. PATCH /api/ttt/v1/reports/&lt;id&gt; with {effort: 120}
-4. DELETE /api/ttt/v1/reports with {ids: [&lt;id&gt;]}</t>
+          <t>1. User A: PATCH report (acquires lock)
+2. User B (within 1 min): PATCH same report
+3. Observe User B error</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>All succeed. REPORTS_EDIT grants full CRUD.
-EDIT condition: reportDate &gt;= report period start AND project not FINISHED.</t>
+          <t>HTTP 423 Locked.
+Error code: exception.ttt.lock.
+TttLockException with lock holder details.</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -7702,49 +7490,47 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr"/>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>TaskReportController, TaskReportPermissionType</t>
+          <t>LockService, RestErrorHandler</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>EDIT = REPORT permission + date in period + project active</t>
+          <t>423 is unique to reports module</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-080</t>
+          <t>TC-RPT-093</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>REPORTS_APPROVE -- state change to APPROVED/REJECTED</t>
+          <t>Error code: exception.ttt.security (403) on permission denied</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>User with REPORTS_APPROVE (PM/SPM/ADMIN on task's project).</t>
+          <t>User without REPORTS_EDIT on target task.</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>1. PATCH /api/ttt/v1/reports/&lt;id&gt; with {state: 'APPROVED'}
-2. PATCH another with {state: 'REJECTED'}
-3. Verify approverLogin set</t>
+          <t>1. POST /api/ttt/v1/reports/create for task without REPORT permission</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Both succeed. REPORTS_APPROVE grants state change rights.
-APPROVE condition: has APPROVE TaskPermissionType + reportDate &gt;= approve period.
-approverLogin set to current user on approve.</t>
+          <t>HTTP 403. Error code: exception.ttt.security.
+TttSecurityException.
+Distinct from AccessDeniedException (which gives FORBIDDEN).</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -7754,47 +7540,48 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr"/>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>TaskReportPermissionType, InternalTaskReportService</t>
+          <t>InternalTaskReportService, RestErrorHandler</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>APPROVE = APPROVE permission + date in approve period</t>
+          <t>Different from vacation's exception.vacation.no.permission</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>TC-RPT-081</t>
+          <t>TC-RPT-094</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>User without REPORTS_EDIT cannot create reports</t>
+          <t>Error code: CONFLICT (409) on duplicate report</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>User with REPORTS_VIEW only (no REPORT TaskPermissionType on task).</t>
+          <t>Existing report for same task+date+executor.</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>1. POST /api/ttt/v1/reports/create for a task where user has VIEW only</t>
+          <t>1. POST duplicate report
+2. Inspect error response</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>HTTP 403. TttSecurityException.
-Error code: exception.ttt.security.
-REPORTS_EDIT requires REPORT permission on the specific task.</t>
+          <t>HTTP 409. Error code: CONFLICT.
+AlreadyExistsException with 'existentObject' field.
+existentObject contains the existing report's ID.</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -7810,46 +7597,46 @@
       <c r="H7" s="11" t="inlineStr"/>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>InternalTaskReportService</t>
+          <t>InternalTaskReportService, RestErrorHandler</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>Per-task permission check</t>
+          <t>Response contains existing report reference</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-082</t>
+          <t>TC-RPT-095</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>User without REPORTS_APPROVE cannot change state</t>
+          <t>Error code: FORBIDDEN (403) on FINISHED project</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Regular employee (no PM role on project).</t>
+          <t>Task on FINISHED project.</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>1. PATCH own report with {state: 'APPROVED'}
-2. Expect error</t>
+          <t>1. POST report for FINISHED project task
+2. Inspect error</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>HTTP 403. Requires APPROVE TaskPermissionType.
-Only PM, Senior PM, ADMIN on the project can approve.</t>
+          <t>HTTP 403. ProjectFinishedException.
+Error code: FORBIDDEN (mapped from ProjectFinishedException).</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -7860,94 +7647,98 @@
       <c r="H8" s="9" t="inlineStr"/>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>InternalTaskReportService</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr"/>
+          <t>RestErrorHandler</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>ProjectFinishedException -&gt; 403</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>TC-RPT-083</t>
+          <t>TC-RPT-096</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>EDIT permission lost when report period closes</t>
+          <t>Error code: BAD_REQUEST (400) with field-level details</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Report with reportDate=2026-02-15. Report period advanced to 2026-03-01.</t>
+          <t>Invalid create request.</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>1. GET report -- check permissions array
-2. PATCH report with {effort: 120}</t>
+          <t>1. POST with missing required fields
+2. Inspect validation error structure</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>permissions array: EDIT absent.
-PATCH returns 403 or permission denied.
-periodState=CLOSED in response.
-EDIT requires reportDate &gt;= report period start.</t>
+          <t>HTTP 400. Error code: BAD_REQUEST.
+MethodArgumentNotValidException provides field-level details.
+Each invalid field listed with violation message.</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr"/>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>TaskReportPermissionType</t>
+          <t>RestErrorHandler</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>Period closure removes EDIT/DELETE permissions</t>
+          <t>ConstraintViolationException also maps to 400</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-084</t>
+          <t>TC-RPT-097</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>APPROVE permission lost when approve period closes</t>
+          <t>ServiceException maps to 500 (inconsistent with vacation's 400)</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Report with reportDate=2026-01-15. Approve period advanced to 2026-02-01.</t>
+          <t>Trigger an internal service error.</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>1. PATCH with {state: 'APPROVED'}
-2. Expect error</t>
+          <t>1. Create scenario causing ServiceException
+2. Observe HTTP status</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>APPROVE permission not granted for reports before approve period.
-Must be: reportDate &gt;= approve period start.</t>
+          <t>HTTP 500. ServiceException maps to INTERNAL_SERVER_ERROR in TTT.
+Inconsistency: same ServiceException maps to 400 in vacation service.
+Different RestErrorHandler implementations per service.</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -7958,93 +7749,94 @@
       <c r="H10" s="9" t="inlineStr"/>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>TaskReportPermissionType</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr"/>
+          <t>RestErrorHandler</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>TTT: 500, Vacation: 400 -- inconsistent across services</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>TC-RPT-085</t>
+          <t>TC-RPT-098</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>BUG: /effort endpoint missing @PreAuthorize</t>
+          <t>Effort boundary: @Min(0) on PATCH allows negative effect via 0</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Unauthenticated or API token request.</t>
+          <t>Existing report.</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>1. GET /api/ttt/v1/reports/effort without JWT
-2. Observe response</t>
+          <t>1. PATCH with {effort: 0} -&gt; deletes report
+2. PATCH with {effort: -1} -&gt; validation error</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>BUG: Endpoint accessible without authentication.
-No @PreAuthorize annotation on /effort endpoint.
-Should require AUTHENTICATED_USER at minimum.</t>
+          <t>effort=0: report deleted (valid, @Min(0)).
+effort=-1: HTTP 400 @Min(0) violation.
+Boundary at 0: deletes. Below 0: rejected.</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Bug verification</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>BUG-REPORT-6</t>
-        </is>
-      </c>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr"/>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>TaskReportController</t>
+          <t>TaskReportEditRequestDTO</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>Missing @PreAuthorize on 2 endpoints</t>
+          <t>Asymmetry: create @Min(1), edit @Min(0)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-086</t>
+          <t>TC-RPT-099</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>BUG: /employee-projects endpoint missing @PreAuthorize</t>
+          <t>Report with effort displayed in hours (÷60 conversion)</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Unauthenticated request.</t>
+          <t>Report with effort=90 minutes.</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>1. GET /api/ttt/v1/reports/employee-projects without JWT
-2. Observe response</t>
+          <t>1. Create report with effort=90
+2. Check UI display in My Tasks
+3. Check API response</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>BUG: Accessible without authentication.
-Same issue as /effort -- missing @PreAuthorize.
-Both endpoints return data without auth check.</t>
+          <t>API: effort=90 (minutes, integer).
+UI: displays 1.5 (hours, effort/60).
+Conversion in frontend: calcEmployeeEffort() divides by 60.</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
@@ -8054,54 +7846,50 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>Bug verification</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>BUG-REPORT-6</t>
-        </is>
-      </c>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr"/>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>TaskReportController</t>
+          <t>frontend-report-module</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>Same bug as TC-RPT-085</t>
+          <t>API uses minutes, UI shows hours</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>TC-RPT-087</t>
+          <t>TC-RPT-100</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Accounting endpoints -- AUTHENTICATED_USER only</t>
+          <t>My Tasks page -- task add via quick search</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>1. JWT authenticated user
-2. API token with permissions</t>
+          <t>Employee on /report page.</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>1. GET /api/ttt/v1/reports/accounting with JWT -&gt; verify access
-2. POST /api/ttt/v1/reports/send-accounting-notifications with JWT
-3. Same endpoints with API_SECRET_TOKEN header</t>
+          <t>1. Click 'Add task' search field
+2. Type task name (partial match)
+3. Select from suggestions
+4. Verify task appears in report grid</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>JWT: both endpoints accessible.
-API token: both return 403.
-Accounting endpoints require AUTHENTICATED_USER (JWT only).</t>
+          <t>TaskAddContainer provides type-ahead search.
+Suggestion endpoint: GET /api/ttt/v1/tasks?search=&lt;query&gt;.
+Selected task added to employee's visible report grid.</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -8111,49 +7899,45 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr"/>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>TaskReportController</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>No API token access to accounting endpoints</t>
-        </is>
-      </c>
+          <t>frontend-report-module, TaskAddContainer</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-088</t>
+          <t>TC-RPT-101</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Warning endpoints -- AUTHENTICATED_USER only</t>
+          <t>My Tasks page -- pin/unpin task for quick access</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>JWT vs API token access.</t>
+          <t>Employee with tasks on /report page.</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>1. GET /api/ttt/v1/task-report-warnings with JWT
-2. GET /api/ttt/v1/task-auto-reject-warnings with JWT
-3. Same with API_SECRET_TOKEN</t>
+          <t>1. Pin a task: POST /api/ttt/v1/tasks/&lt;id&gt;/employees/&lt;login&gt;/pin
+2. Verify task appears at top of list
+3. Unpin: DELETE /api/ttt/v1/tasks/&lt;id&gt;/employees/&lt;login&gt;/pin</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>JWT: accessible. API token: 403.
-Warning endpoints require AUTHENTICATED_USER.
-Auto-reject controller returns BO directly (no DTO -- design issue).</t>
+          <t>Pinned tasks appear at top of My Tasks table.
+Pin persists across sessions.
+Unpin removes from pinned list.</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -8163,49 +7947,49 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>TaskReportWarningController, TaskReportAutoRejectController</t>
+          <t>frontend-report-module</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>Auto-reject returns BO instead of DTO (BO leak)</t>
+          <t>Pin/unpin via POST/DELETE endpoints</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>TC-RPT-089</t>
+          <t>TC-RPT-102</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Permission calculation flow -- per-task, per-report</t>
+          <t>My Tasks page -- week switcher navigation</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>User with PM role on Project A, employee on Project B.</t>
+          <t>Employee on /report page.</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>1. GET reports for tasks on Project A
-2. GET reports for tasks on Project B
-3. Compare permissions arrays</t>
+          <t>1. Click previous/next week arrows
+2. Observe date range update
+3. Verify reports refresh for new week</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Project A reports: permissions include EDIT, DELETE, APPROVE.
-Project B reports: permissions include EDIT, DELETE only.
-Permissions calculated: group by executor → by task → per report.</t>
+          <t>Week navigation with left/right arrows.
+Shows Monday-Sunday range.
+Complex date math with Moment.js (tech debt -- should use date-fns).</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -8221,48 +8005,47 @@
       <c r="H15" s="11" t="inlineStr"/>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>TaskReportPermissionType</t>
+          <t>frontend-report-module, WeekSwitcherContainer</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>Per-task permission, not global</t>
+          <t>Moment.js tech debt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>TC-RPT-090</t>
+          <t>TC-RPT-103</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Auth polling -- excessive /authentication/check calls</t>
+          <t>My Tasks page -- grouped by project vs ungrouped toggle</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Open Confirmation page in browser with network monitor.</t>
+          <t>Employee with tasks across multiple projects.</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>1. Navigate to /approve
-2. Monitor network tab for 60 seconds
-3. Count GET /v1/authentication/check calls</t>
+          <t>1. Toggle 'Grouped by project' switch
+2. Verify table layout changes</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>50+ GET /v1/authentication/check calls per session.
-Excessive auth polling pattern.
-Performance concern but functionally harmless.</t>
+          <t>Ungrouped: flat task list.
+Grouped: tasks organized under project headers.
+Toggle state persisted in Redux uiFiltersReducer.</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -8273,17 +8056,372 @@
       <c r="H16" s="9" t="inlineStr"/>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>frontend-approve-module</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>Performance: excessive auth polling</t>
+          <t>frontend-report-module, ProjectsGroupedSwitcher</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>TC-RPT-104</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Report event system -- add/patch/delete events published</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Create, edit, delete reports.</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>1. POST /api/ttt/v1/reports/create -&gt; TaskReportAddEvent
+2. PATCH /api/ttt/v1/reports/&lt;id&gt; -&gt; TaskReportPatchEvent
+3. DELETE -&gt; TaskReportDeleteEvent (also via effort=0)</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Three event types published:
+- TaskReportAddEvent: on creation
+- TaskReportPatchEvent: on update (with before-state)
+- TaskReportDeleteEvent: on delete AND on effort=0
+Events drive: statistics cache, audit trail, notifications.</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr"/>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>TaskReportEventListener</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>Async + transactional event listener</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>TC-RPT-105</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Accounting notifications -- send reminders to employees</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Accountant on accounting page with unconfirmed reports.</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>1. POST /api/ttt/v1/reports/send-accounting-notifications
+2. Check emails sent</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Sends reminder notifications to employees with unconfirmed hours.
+Accountant-initiated action (not scheduled).
+AUTHENTICATED_USER only (no API token).</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>TaskReportController</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>Manual trigger by accountant</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>TC-RPT-106</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>GET /reports/accounting -- paginated by office and date range</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Accountant JWT auth.</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>1. GET /api/ttt/v1/reports/accounting?officeId=&lt;id&gt;&amp;from=2026-03-01&amp;to=2026-03-31
+2. Verify pagination structure</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Paginated response filtered by office and date range.
+Used by accountant confirmation view.
+JWT only -- API token returns 403.</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>TaskReportController</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>TC-RPT-107</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Hardcoded CEO login in statistics -- ilnitsky</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Code inspection / behavior verification.</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>1. Check StatisticReportService for CEO_LOGIN constant
+2. Verify special handling for CEO login</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Hardcoded: CEO_LOGIN = 'ilnitsky'.
+CEO excluded from certain statistics calculations.
+Design issue: hardcoded login instead of role-based check.</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>StatisticReportService</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>Hardcoded CEO login -- design debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>TC-RPT-108</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Daily report effort limit -- 36h (2160 minutes) warning threshold</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Employee reporting &gt;36h on a single day.</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>1. Create reports totaling &gt;2160 min on one day
+2. Check for warning generation</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Warning type: DATE_EFFORT_OVER_LIMIT generated.
+36h = 2160 minutes per day threshold.
+Warning only -- does not prevent report creation.</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>TaskReportWarningController</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>Warning only, not enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>TC-RPT-109</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>DTO response structure -- all fields verified</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Create a report and inspect full response.</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>1. POST /api/ttt/v1/reports/create
+2. Inspect response JSON structure</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Response DTO fields:
+- id (Long), state (REPORTED|APPROVED|REJECTED)
+- stateComment (null unless REJECTED)
+- effort (Long, minutes), reportDate (ISO date)
+- executorLogin, reporterLogin, approverLogin
+- periodState (OPEN|CLOSED), reportComment
+- projectState {id, name, status}
+- permissions[] (EDIT, DELETE, APPROVE subset)</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr"/>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>TaskReportDTO</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>TC-RPT-110</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Reject response shows approverLogin derived from reject.rejector</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Report in REJECTED state.</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>1. Reject a report with known rejector
+2. GET report via search
+3. Check approverLogin field</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>API response shows approverLogin for rejected reports.
+But DB column task_report.approver is NULL.
+Value derived from reject.rejector (join query).
+Confusing: field named 'approver' but shows rejector.</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr"/>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>InternalTaskReportService</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>Naming confusion: approverLogin shows rejector on rejected reports</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J16"/>
+  <autoFilter ref="A3:J23"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
   </hyperlinks>
